--- a/data-raw/public-site/moa-machine-county/xlsx/case-year-2021-batch01.xlsx
+++ b/data-raw/public-site/moa-machine-county/xlsx/case-year-2021-batch01.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">上海设施中棵青梗菜机械化生产模式与典型案例</t>
   </si>
   <si>
-    <t xml:space="preserve">中棵青梗菜</t>
+    <t xml:space="preserve">青梗菜</t>
   </si>
   <si>
     <t xml:space="preserve">北京设施果菜机械化生产模式与典型案例</t>
